--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114972378</v>
+        <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
+        <v>96859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alefjäll, Vg</t>
+          <t>Älefjäll mitten, Älefjäll mitten, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334615</v>
+        <v>334592</v>
       </c>
       <c r="R2" t="n">
-        <v>6418970</v>
+        <v>6418982</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114972378</t>
+          <t>https://artportalen.se/Sighting/135887810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114972379</v>
+        <v>114972378</v>
       </c>
       <c r="B3" t="n">
         <v>96348</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334581</v>
+        <v>334615</v>
       </c>
       <c r="R3" t="n">
-        <v>6418933</v>
+        <v>6418970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,16 +888,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114972379</t>
+          <t>https://artportalen.se/Sighting/114972378</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114972389</v>
+        <v>114972379</v>
       </c>
       <c r="B4" t="n">
-        <v>97983</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334580</v>
+        <v>334581</v>
       </c>
       <c r="R4" t="n">
-        <v>6419177</v>
+        <v>6418933</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +989,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972379</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114972389</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334580</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419177</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114972389</t>
         </is>
@@ -989,6 +1101,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114972378</v>
+        <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alefjäll, Vg</t>
+          <t>Älefjäll mitten, Älefjäll mitten, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334615</v>
+        <v>334587</v>
       </c>
       <c r="R3" t="n">
-        <v>6418970</v>
+        <v>6418965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 kuddar invid bäcken, den största ca 30cm diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +892,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114972378</t>
+          <t>https://artportalen.se/Sighting/136021596</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114972379</v>
+        <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
+        <v>96861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Alefjäll, Vg</t>
+          <t>Kilanda, Kilanda, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334581</v>
+        <v>334588</v>
       </c>
       <c r="R4" t="n">
-        <v>6418933</v>
+        <v>6418886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +1004,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114972379</t>
+          <t>https://artportalen.se/Sighting/136023776</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114972389</v>
+        <v>114972378</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334580</v>
+        <v>334615</v>
       </c>
       <c r="R5" t="n">
-        <v>6419177</v>
+        <v>6418970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,6 +1116,440 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972378</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114972379</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334581</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6418933</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972379</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136023611</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kilanda, Kilanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334588</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6418886</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136023611</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136021644</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98132</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Älefjäll mitten, Älefjäll mitten, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334587</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6418965</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På häll nära bäcken med smågranar, troligtvis äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136021644</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114972389</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>334580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6419177</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114972389</t>
         </is>
@@ -1102,6 +1561,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136023611</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136021644</v>
       </c>
       <c r="B8" t="n">
-        <v>98132</v>
+        <v>98149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1225,27 +1225,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136023611</v>
+        <v>136136856</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1254,21 +1254,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kilanda, Kilanda, Vg</t>
+          <t>Alefjäll Mitten, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334588</v>
+        <v>334595</v>
       </c>
       <c r="R7" t="n">
-        <v>6418886</v>
+        <v>6418990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,22 +1294,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inspelad på platsen med passiv ljudinspelning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,16 +1340,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136023611</t>
+          <t>https://artportalen.se/Sighting/136136856</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136021644</v>
+        <v>136023611</v>
       </c>
       <c r="B8" t="n">
-        <v>98149</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,30 +1357,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älefjäll mitten, Älefjäll mitten, Vg</t>
+          <t>Kilanda, Kilanda, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334587</v>
+        <v>334588</v>
       </c>
       <c r="R8" t="n">
-        <v>6418965</v>
+        <v>6418886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På häll nära bäcken med smågranar, troligtvis äkta lopplummer</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,51 +1457,55 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136021644</t>
+          <t>https://artportalen.se/Sighting/136023611</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114972389</v>
+        <v>136136720</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>58143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Alefjäll, Vg</t>
+          <t>Alefjäll Mitten, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334580</v>
+        <v>334634</v>
       </c>
       <c r="R9" t="n">
-        <v>6419177</v>
+        <v>6418863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,12 +1532,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med Audiomoth</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,16 +1567,352 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136136720</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136136941</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alefjäll Mitten, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334595</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6418990</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inspelad i fält med passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136136941</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136021644</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98149</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Älefjäll mitten, Älefjäll mitten, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>334587</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6418965</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På häll nära bäcken med smågranar, troligtvis äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136021644</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114972389</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>334580</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6419177</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114972389</t>
         </is>
@@ -1565,6 +1928,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98149</v>
+        <v>98150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98150</v>
+        <v>98151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136136856</v>
       </c>
       <c r="B7" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136023611</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136136720</v>
       </c>
       <c r="B9" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136136941</v>
       </c>
       <c r="B10" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98151</v>
+        <v>98152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136136856</v>
       </c>
       <c r="B7" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136023611</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136136720</v>
       </c>
       <c r="B9" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136136941</v>
       </c>
       <c r="B10" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98152</v>
+        <v>98158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135887810</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136136856</v>
       </c>
       <c r="B7" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136023611</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136136720</v>
       </c>
       <c r="B9" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136136941</v>
       </c>
       <c r="B10" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
